--- a/samples/BK_SalesData_BKDS_2026-06.xlsx
+++ b/samples/BK_SalesData_BKDS_2026-06.xlsx
@@ -439,10 +439,10 @@
         <v>OCCUPANCY</v>
       </c>
       <c r="B2">
-        <v>0.84</v>
+        <v>0.8407</v>
       </c>
       <c r="C2">
-        <v>0.9</v>
+        <v>0.9019</v>
       </c>
       <c r="D2" t="str">
         <v/>
